--- a/assets/A类授信调整.xlsx
+++ b/assets/A类授信调整.xlsx
@@ -7,13 +7,10 @@
     <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
-    <sheet name="1月批量调整 (2)" sheetId="4" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
+    <sheet name="授信调整表" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'1月批量调整 (2)'!$2:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">授信调整表!$2:$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>附件1</t>
   </si>
@@ -62,55 +59,7 @@
     <t>授信总额</t>
   </si>
   <si>
-    <t>华夏银行股份有限公司</t>
-  </si>
-  <si>
-    <t>江苏常熟农村商业银行股份有限公司</t>
-  </si>
-  <si>
-    <t>江苏江南农村商业银行股份有限公司</t>
-  </si>
-  <si>
-    <t>交通银行股份有限公司</t>
-  </si>
-  <si>
-    <t>中国民生银行股份有限公司</t>
-  </si>
-  <si>
-    <t>宁波银行股份有限公司</t>
-  </si>
-  <si>
-    <t>中国农业银行股份有限公司</t>
-  </si>
-  <si>
-    <t>平安银行股份有限公司</t>
-  </si>
-  <si>
-    <t>上海农村商业银行股份有限公司</t>
-  </si>
-  <si>
-    <t>上海浦东发展银行股份有限公司</t>
-  </si>
-  <si>
-    <t>上海银行股份有限公司</t>
-  </si>
-  <si>
-    <t>台州银行股份有限公司</t>
-  </si>
-  <si>
-    <t>招商银行股份有限公司</t>
-  </si>
-  <si>
-    <t>中国工商银行股份有限公司</t>
-  </si>
-  <si>
-    <t>中国光大银行股份有限公司</t>
-  </si>
-  <si>
-    <t>中国银行股份有限公司</t>
-  </si>
-  <si>
-    <t>中信银行股份有限公司</t>
+    <t>浙江萧山农商银行股份有限公司</t>
   </si>
   <si>
     <t>合计</t>
@@ -1415,12 +1364,8 @@
       <c r="W6" s="11"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
-      <c r="A7" s="11">
-        <v>2</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>10</v>
-      </c>
+      <c r="A7" s="11"/>
+      <c r="B7" s="14"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
@@ -1444,12 +1389,8 @@
       <c r="W7" s="11"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
-      <c r="A8" s="11">
-        <v>3</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>11</v>
-      </c>
+      <c r="A8" s="11"/>
+      <c r="B8" s="14"/>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
@@ -1473,12 +1414,8 @@
       <c r="W8" s="11"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
-      <c r="A9" s="11">
-        <v>4</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>12</v>
-      </c>
+      <c r="A9" s="11"/>
+      <c r="B9" s="14"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
@@ -1502,12 +1439,8 @@
       <c r="W9" s="11"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
-      <c r="A10" s="11">
-        <v>5</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>13</v>
-      </c>
+      <c r="A10" s="11"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -1531,12 +1464,8 @@
       <c r="W10" s="11"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
-      <c r="A11" s="11">
-        <v>6</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>14</v>
-      </c>
+      <c r="A11" s="11"/>
+      <c r="B11" s="14"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
@@ -1560,12 +1489,8 @@
       <c r="W11" s="11"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
-      <c r="A12" s="11">
-        <v>7</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>15</v>
-      </c>
+      <c r="A12" s="11"/>
+      <c r="B12" s="14"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
@@ -1589,12 +1514,8 @@
       <c r="W12" s="11"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
-      <c r="A13" s="11">
-        <v>8</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>16</v>
-      </c>
+      <c r="A13" s="11"/>
+      <c r="B13" s="14"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
@@ -1618,12 +1539,8 @@
       <c r="W13" s="11"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
-      <c r="A14" s="11">
-        <v>9</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>17</v>
-      </c>
+      <c r="A14" s="11"/>
+      <c r="B14" s="14"/>
       <c r="C14" s="15"/>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
@@ -1647,12 +1564,8 @@
       <c r="W14" s="11"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
-      <c r="A15" s="11">
-        <v>10</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>18</v>
-      </c>
+      <c r="A15" s="11"/>
+      <c r="B15" s="14"/>
       <c r="C15" s="16"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
@@ -1676,12 +1589,8 @@
       <c r="W15" s="17"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
-      <c r="A16" s="11">
-        <v>11</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>19</v>
-      </c>
+      <c r="A16" s="11"/>
+      <c r="B16" s="14"/>
       <c r="C16" s="16"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17"/>
@@ -1705,12 +1614,8 @@
       <c r="W16" s="17"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
-      <c r="A17" s="11">
-        <v>12</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>20</v>
-      </c>
+      <c r="A17" s="11"/>
+      <c r="B17" s="14"/>
       <c r="C17" s="16"/>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
@@ -1734,12 +1639,8 @@
       <c r="W17" s="17"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
-      <c r="A18" s="11">
-        <v>13</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>21</v>
-      </c>
+      <c r="A18" s="11"/>
+      <c r="B18" s="14"/>
       <c r="C18" s="16"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
@@ -1763,12 +1664,8 @@
       <c r="W18" s="17"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
-      <c r="A19" s="11">
-        <v>14</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>22</v>
-      </c>
+      <c r="A19" s="11"/>
+      <c r="B19" s="14"/>
       <c r="C19" s="15"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
@@ -1792,12 +1689,8 @@
       <c r="W19" s="17"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
-      <c r="A20" s="11">
-        <v>15</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>23</v>
-      </c>
+      <c r="A20" s="11"/>
+      <c r="B20" s="14"/>
       <c r="C20" s="16"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
@@ -1821,12 +1714,8 @@
       <c r="W20" s="17"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
-      <c r="A21" s="11">
-        <v>16</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>24</v>
-      </c>
+      <c r="A21" s="11"/>
+      <c r="B21" s="14"/>
       <c r="C21" s="15"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
@@ -1850,12 +1739,8 @@
       <c r="W21" s="17"/>
     </row>
     <row r="22" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
-      <c r="A22" s="11">
-        <v>17</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>25</v>
-      </c>
+      <c r="A22" s="11"/>
+      <c r="B22" s="14"/>
       <c r="C22" s="16"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
@@ -1881,7 +1766,7 @@
     <row r="23" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
       <c r="A23" s="11"/>
       <c r="B23" s="14" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C23" s="11"/>
       <c r="D23" s="17"/>
@@ -1907,11 +1792,11 @@
     </row>
     <row r="24" s="2" customFormat="1" ht="54" customHeight="1" spans="1:23">
       <c r="A24" s="14" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="18" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
@@ -1936,7 +1821,7 @@
     </row>
     <row r="25" s="2" customFormat="1" ht="54" customHeight="1" spans="1:23">
       <c r="A25" s="14" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="21"/>
@@ -1963,7 +1848,7 @@
     </row>
     <row r="26" ht="54" customHeight="1" spans="1:23">
       <c r="A26" s="14" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="21"/>
@@ -1990,7 +1875,7 @@
     </row>
     <row r="27" ht="54" customHeight="1" spans="1:23">
       <c r="A27" s="14" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="21"/>
@@ -2017,7 +1902,7 @@
     </row>
     <row r="28" ht="54" customHeight="1" spans="1:23">
       <c r="A28" s="14" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="21"/>
@@ -2076,40 +1961,4 @@
   <pageSetup paperSize="9" scale="90" fitToHeight="2" orientation="landscape" horizontalDpi="600"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/assets/A类授信调整.xlsx
+++ b/assets/A类授信调整.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>附件1</t>
   </si>
@@ -59,7 +59,10 @@
     <t>授信总额</t>
   </si>
   <si>
-    <t>浙江萧山农商银行股份有限公司</t>
+    <t>浙江萧山农村商业银行股份有限公司</t>
+  </si>
+  <si>
+    <t>北京银行股份有限公司</t>
   </si>
   <si>
     <t>合计</t>
@@ -93,7 +96,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,6 +130,12 @@
       <sz val="8"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -472,7 +481,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -517,6 +526,21 @@
       </right>
       <top/>
       <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -676,137 +700,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="13">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="14">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -852,17 +876,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -870,13 +894,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1365,7 +1392,9 @@
     </row>
     <row r="7" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
       <c r="A7" s="11"/>
-      <c r="B7" s="14"/>
+      <c r="B7" s="15" t="s">
+        <v>10</v>
+      </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
@@ -1541,7 +1570,7 @@
     <row r="14" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
       <c r="A14" s="11"/>
       <c r="B14" s="14"/>
-      <c r="C14" s="15"/>
+      <c r="C14" s="16"/>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
@@ -1566,374 +1595,374 @@
     <row r="15" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
       <c r="A15" s="11"/>
       <c r="B15" s="14"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="17"/>
-      <c r="T15" s="17"/>
-      <c r="U15" s="17"/>
-      <c r="V15" s="17"/>
-      <c r="W15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="18"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="18"/>
+      <c r="V15" s="18"/>
+      <c r="W15" s="18"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
       <c r="A16" s="11"/>
       <c r="B16" s="14"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="17"/>
-      <c r="T16" s="17"/>
-      <c r="U16" s="17"/>
-      <c r="V16" s="17"/>
-      <c r="W16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="18"/>
+      <c r="Q16" s="18"/>
+      <c r="R16" s="18"/>
+      <c r="S16" s="18"/>
+      <c r="T16" s="18"/>
+      <c r="U16" s="18"/>
+      <c r="V16" s="18"/>
+      <c r="W16" s="18"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
       <c r="A17" s="11"/>
       <c r="B17" s="14"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="17"/>
-      <c r="T17" s="17"/>
-      <c r="U17" s="17"/>
-      <c r="V17" s="17"/>
-      <c r="W17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="18"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="18"/>
+      <c r="T17" s="18"/>
+      <c r="U17" s="18"/>
+      <c r="V17" s="18"/>
+      <c r="W17" s="18"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
       <c r="A18" s="11"/>
       <c r="B18" s="14"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="17"/>
-      <c r="T18" s="17"/>
-      <c r="U18" s="17"/>
-      <c r="V18" s="17"/>
-      <c r="W18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="18"/>
+      <c r="R18" s="18"/>
+      <c r="S18" s="18"/>
+      <c r="T18" s="18"/>
+      <c r="U18" s="18"/>
+      <c r="V18" s="18"/>
+      <c r="W18" s="18"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
       <c r="A19" s="11"/>
       <c r="B19" s="14"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="17"/>
-      <c r="T19" s="17"/>
-      <c r="U19" s="17"/>
-      <c r="V19" s="17"/>
-      <c r="W19" s="17"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="18"/>
+      <c r="R19" s="18"/>
+      <c r="S19" s="18"/>
+      <c r="T19" s="18"/>
+      <c r="U19" s="18"/>
+      <c r="V19" s="18"/>
+      <c r="W19" s="18"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
       <c r="A20" s="11"/>
       <c r="B20" s="14"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
-      <c r="R20" s="17"/>
-      <c r="S20" s="17"/>
-      <c r="T20" s="17"/>
-      <c r="U20" s="17"/>
-      <c r="V20" s="17"/>
-      <c r="W20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="18"/>
+      <c r="R20" s="18"/>
+      <c r="S20" s="18"/>
+      <c r="T20" s="18"/>
+      <c r="U20" s="18"/>
+      <c r="V20" s="18"/>
+      <c r="W20" s="18"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
       <c r="A21" s="11"/>
       <c r="B21" s="14"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17"/>
-      <c r="S21" s="17"/>
-      <c r="T21" s="17"/>
-      <c r="U21" s="17"/>
-      <c r="V21" s="17"/>
-      <c r="W21" s="17"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="18"/>
+      <c r="S21" s="18"/>
+      <c r="T21" s="18"/>
+      <c r="U21" s="18"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="18"/>
     </row>
     <row r="22" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
       <c r="A22" s="11"/>
       <c r="B22" s="14"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="17"/>
-      <c r="T22" s="17"/>
-      <c r="U22" s="17"/>
-      <c r="V22" s="17"/>
-      <c r="W22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="18"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="18"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="18"/>
+      <c r="V22" s="18"/>
+      <c r="W22" s="18"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="30" customHeight="1" spans="1:23">
       <c r="A23" s="11"/>
       <c r="B23" s="14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" s="11"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="17"/>
-      <c r="S23" s="17"/>
-      <c r="T23" s="17"/>
-      <c r="U23" s="17"/>
-      <c r="V23" s="17"/>
-      <c r="W23" s="17"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="18"/>
+      <c r="R23" s="18"/>
+      <c r="S23" s="18"/>
+      <c r="T23" s="18"/>
+      <c r="U23" s="18"/>
+      <c r="V23" s="18"/>
+      <c r="W23" s="18"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="54" customHeight="1" spans="1:23">
       <c r="A24" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B24" s="14"/>
-      <c r="C24" s="18" t="s">
-        <v>12</v>
+      <c r="C24" s="19" t="s">
+        <v>13</v>
       </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="19"/>
-      <c r="U24" s="19"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="20"/>
+      <c r="W24" s="21"/>
     </row>
     <row r="25" s="2" customFormat="1" ht="54" customHeight="1" spans="1:23">
       <c r="A25" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B25" s="14"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="22"/>
-      <c r="R25" s="22"/>
-      <c r="S25" s="22"/>
-      <c r="T25" s="22"/>
-      <c r="U25" s="22"/>
-      <c r="V25" s="22"/>
-      <c r="W25" s="23"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="23"/>
+      <c r="P25" s="23"/>
+      <c r="Q25" s="23"/>
+      <c r="R25" s="23"/>
+      <c r="S25" s="23"/>
+      <c r="T25" s="23"/>
+      <c r="U25" s="23"/>
+      <c r="V25" s="23"/>
+      <c r="W25" s="24"/>
     </row>
     <row r="26" ht="54" customHeight="1" spans="1:23">
       <c r="A26" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B26" s="14"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="22"/>
-      <c r="O26" s="22"/>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="22"/>
-      <c r="R26" s="22"/>
-      <c r="S26" s="22"/>
-      <c r="T26" s="22"/>
-      <c r="U26" s="22"/>
-      <c r="V26" s="22"/>
-      <c r="W26" s="23"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="23"/>
+      <c r="O26" s="23"/>
+      <c r="P26" s="23"/>
+      <c r="Q26" s="23"/>
+      <c r="R26" s="23"/>
+      <c r="S26" s="23"/>
+      <c r="T26" s="23"/>
+      <c r="U26" s="23"/>
+      <c r="V26" s="23"/>
+      <c r="W26" s="24"/>
     </row>
     <row r="27" ht="54" customHeight="1" spans="1:23">
       <c r="A27" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B27" s="14"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="22"/>
-      <c r="N27" s="22"/>
-      <c r="O27" s="22"/>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="22"/>
-      <c r="R27" s="22"/>
-      <c r="S27" s="22"/>
-      <c r="T27" s="22"/>
-      <c r="U27" s="22"/>
-      <c r="V27" s="22"/>
-      <c r="W27" s="23"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="23"/>
+      <c r="O27" s="23"/>
+      <c r="P27" s="23"/>
+      <c r="Q27" s="23"/>
+      <c r="R27" s="23"/>
+      <c r="S27" s="23"/>
+      <c r="T27" s="23"/>
+      <c r="U27" s="23"/>
+      <c r="V27" s="23"/>
+      <c r="W27" s="24"/>
     </row>
     <row r="28" ht="54" customHeight="1" spans="1:23">
       <c r="A28" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B28" s="14"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="22"/>
-      <c r="O28" s="22"/>
-      <c r="P28" s="22"/>
-      <c r="Q28" s="22"/>
-      <c r="R28" s="22"/>
-      <c r="S28" s="22"/>
-      <c r="T28" s="22"/>
-      <c r="U28" s="22"/>
-      <c r="V28" s="22"/>
-      <c r="W28" s="23"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
+      <c r="T28" s="23"/>
+      <c r="U28" s="23"/>
+      <c r="V28" s="23"/>
+      <c r="W28" s="24"/>
     </row>
     <row r="29" spans="1:23">
-      <c r="A29" s="24"/>
-      <c r="B29" s="24"/>
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
     </row>
     <row r="30" spans="1:23">
-      <c r="A30" s="24"/>
-      <c r="B30" s="24"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="18">
